--- a/wedding_forms/017_marriage_registration_form_template--wedding_forms.xlsx
+++ b/wedding_forms/017_marriage_registration_form_template--wedding_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -869,12 +869,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>marriage_place</t>
+          <t>marriage_place_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Marriage Place</t>
+          <t>Marriage Place 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -892,12 +892,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>marriage_date</t>
+          <t>marriage_date_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Marriage Date</t>
+          <t>Marriage Date 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -961,12 +961,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>marriage_certificate_number</t>
+          <t>marriage_certificate_number_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Marriage Certificate Number</t>
+          <t>Marriage Certificate Number 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
